--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY256"/>
+  <dimension ref="A1:AY258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33067,6 +33067,246 @@
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>113689368</v>
+      </c>
+      <c r="B257" t="n">
+        <v>97396</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>432683</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6485874</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Binneberg</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>Blandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>113689369</v>
+      </c>
+      <c r="B258" t="n">
+        <v>97396</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>432662</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6485797</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Binneberg</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>Blandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -33072,7 +33072,7 @@
         <v>113689368</v>
       </c>
       <c r="B257" t="n">
-        <v>97396</v>
+        <v>97398</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>113689369</v>
       </c>
       <c r="B258" t="n">
-        <v>97396</v>
+        <v>97398</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -33072,7 +33072,7 @@
         <v>113689368</v>
       </c>
       <c r="B257" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>113689369</v>
       </c>
       <c r="B258" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -33069,7 +33069,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>113689368</v>
+        <v>113689369</v>
       </c>
       <c r="B257" t="n">
         <v>97402</v>
@@ -33104,7 +33104,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -33121,10 +33121,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>432683</v>
+        <v>432662</v>
       </c>
       <c r="R257" t="n">
-        <v>6485874</v>
+        <v>6485797</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -33189,7 +33189,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>113689369</v>
+        <v>113689368</v>
       </c>
       <c r="B258" t="n">
         <v>97402</v>
@@ -33224,7 +33224,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -33241,10 +33241,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>432662</v>
+        <v>432683</v>
       </c>
       <c r="R258" t="n">
-        <v>6485797</v>
+        <v>6485874</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -33069,7 +33069,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>113689369</v>
+        <v>113689368</v>
       </c>
       <c r="B257" t="n">
         <v>97402</v>
@@ -33104,7 +33104,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -33121,10 +33121,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>432662</v>
+        <v>432683</v>
       </c>
       <c r="R257" t="n">
-        <v>6485797</v>
+        <v>6485874</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -33189,7 +33189,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>113689368</v>
+        <v>113689369</v>
       </c>
       <c r="B258" t="n">
         <v>97402</v>
@@ -33224,7 +33224,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -33241,10 +33241,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>432683</v>
+        <v>432662</v>
       </c>
       <c r="R258" t="n">
-        <v>6485874</v>
+        <v>6485797</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12027-2022 artfynd.xlsx
+++ b/artfynd/A 12027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY258"/>
+  <dimension ref="A1:AY255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16712,7 +16712,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103213723</v>
+        <v>103216817</v>
       </c>
       <c r="B128" t="n">
         <v>96334</v>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16767,13 +16767,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>432285.1659366059</v>
+        <v>432285.6803057679</v>
       </c>
       <c r="R128" t="n">
-        <v>6485788.770066185</v>
+        <v>6485788.238567303</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18232,7 +18232,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>103216817</v>
+        <v>103214967</v>
       </c>
       <c r="B140" t="n">
         <v>96334</v>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -18287,10 +18287,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>432285.6803057679</v>
+        <v>432297.1410293173</v>
       </c>
       <c r="R140" t="n">
-        <v>6485788.238567303</v>
+        <v>6485784.904732605</v>
       </c>
       <c r="S140" t="n">
         <v>2</v>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18359,7 +18359,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>103214967</v>
+        <v>103215893</v>
       </c>
       <c r="B141" t="n">
         <v>96334</v>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -18414,10 +18414,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>432297.1410293173</v>
+        <v>432281.6918812259</v>
       </c>
       <c r="R141" t="n">
-        <v>6485784.904732605</v>
+        <v>6485799.804778186</v>
       </c>
       <c r="S141" t="n">
         <v>2</v>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18486,7 +18486,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>103215893</v>
+        <v>103216700</v>
       </c>
       <c r="B142" t="n">
         <v>96334</v>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>432281.6918812259</v>
+        <v>432288.116604658</v>
       </c>
       <c r="R142" t="n">
-        <v>6485799.804778186</v>
+        <v>6485777.744379946</v>
       </c>
       <c r="S142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -18613,7 +18613,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>103216700</v>
+        <v>103216028</v>
       </c>
       <c r="B143" t="n">
         <v>96334</v>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -18668,13 +18668,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>432288.116604658</v>
+        <v>432273.948446459</v>
       </c>
       <c r="R143" t="n">
-        <v>6485777.744379946</v>
+        <v>6485775.899055228</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18740,7 +18740,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>103216028</v>
+        <v>103215087</v>
       </c>
       <c r="B144" t="n">
         <v>96334</v>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18795,13 +18795,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>432273.948446459</v>
+        <v>432283.912020534</v>
       </c>
       <c r="R144" t="n">
-        <v>6485775.899055228</v>
+        <v>6485807.082768598</v>
       </c>
       <c r="S144" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18867,7 +18867,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>103215087</v>
+        <v>103213544</v>
       </c>
       <c r="B145" t="n">
         <v>96334</v>
@@ -18922,13 +18922,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>432283.912020534</v>
+        <v>432264.9781959144</v>
       </c>
       <c r="R145" t="n">
-        <v>6485807.082768598</v>
+        <v>6485771.873424458</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18994,7 +18994,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>103213544</v>
+        <v>103242078</v>
       </c>
       <c r="B146" t="n">
         <v>96334</v>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -19045,14 +19045,14 @@
       <c r="L146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>432264.9781959144</v>
+        <v>432261.4960660134</v>
       </c>
       <c r="R146" t="n">
-        <v>6485771.873424458</v>
+        <v>6485812.696571696</v>
       </c>
       <c r="S146" t="n">
         <v>2</v>
@@ -19079,22 +19079,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-08-28</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-08-28</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -19121,7 +19121,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>103242078</v>
+        <v>103240712</v>
       </c>
       <c r="B147" t="n">
         <v>96334</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -19176,13 +19176,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>432261.4960660134</v>
+        <v>432268.6528355109</v>
       </c>
       <c r="R147" t="n">
-        <v>6485812.696571696</v>
+        <v>6485832.954028109</v>
       </c>
       <c r="S147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -19248,7 +19248,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>103240712</v>
+        <v>103241691</v>
       </c>
       <c r="B148" t="n">
         <v>96334</v>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -19299,17 +19299,17 @@
       <c r="L148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>432268.6528355109</v>
+        <v>432267.5870745999</v>
       </c>
       <c r="R148" t="n">
-        <v>6485832.954028109</v>
+        <v>6485801.616595513</v>
       </c>
       <c r="S148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -19375,7 +19375,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>103241691</v>
+        <v>103240458</v>
       </c>
       <c r="B149" t="n">
         <v>96334</v>
@@ -19410,7 +19410,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -19426,14 +19426,14 @@
       <c r="L149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>432267.5870745999</v>
+        <v>432267.8130585536</v>
       </c>
       <c r="R149" t="n">
-        <v>6485801.616595513</v>
+        <v>6485814.677662788</v>
       </c>
       <c r="S149" t="n">
         <v>2</v>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -19502,7 +19502,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>103240458</v>
+        <v>103241900</v>
       </c>
       <c r="B150" t="n">
         <v>96334</v>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -19557,13 +19557,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>432267.8130585536</v>
+        <v>432261.5141463919</v>
       </c>
       <c r="R150" t="n">
-        <v>6485814.677662788</v>
+        <v>6485813.741455738</v>
       </c>
       <c r="S150" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -19629,7 +19629,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>103241900</v>
+        <v>103241384</v>
       </c>
       <c r="B151" t="n">
         <v>96334</v>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -19680,17 +19680,17 @@
       <c r="L151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>432261.5141463919</v>
+        <v>432272.4965663009</v>
       </c>
       <c r="R151" t="n">
-        <v>6485813.741455738</v>
+        <v>6485813.028836064</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -19756,7 +19756,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103241384</v>
+        <v>103240830</v>
       </c>
       <c r="B152" t="n">
         <v>96334</v>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -19807,14 +19807,14 @@
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>432272.4965663009</v>
+        <v>432266.3965229811</v>
       </c>
       <c r="R152" t="n">
-        <v>6485813.028836064</v>
+        <v>6485823.586331926</v>
       </c>
       <c r="S152" t="n">
         <v>2</v>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -19883,7 +19883,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>103240830</v>
+        <v>103240537</v>
       </c>
       <c r="B153" t="n">
         <v>96334</v>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -19938,10 +19938,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>432266.3965229811</v>
+        <v>432270.3939158259</v>
       </c>
       <c r="R153" t="n">
-        <v>6485823.586331926</v>
+        <v>6485812.542615937</v>
       </c>
       <c r="S153" t="n">
         <v>2</v>
@@ -19973,7 +19973,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20010,7 +20010,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>103240537</v>
+        <v>103257818</v>
       </c>
       <c r="B154" t="n">
         <v>96334</v>
@@ -20045,19 +20045,10 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -20065,10 +20056,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>432270.3939158259</v>
+        <v>432215.5064235844</v>
       </c>
       <c r="R154" t="n">
-        <v>6485812.542615937</v>
+        <v>6485757.051572653</v>
       </c>
       <c r="S154" t="n">
         <v>2</v>
@@ -20095,22 +20086,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2022-08-28</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2022-08-28</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20137,7 +20128,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>103257818</v>
+        <v>103259400</v>
       </c>
       <c r="B155" t="n">
         <v>96334</v>
@@ -20172,10 +20163,19 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -20183,10 +20183,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>432215.5064235844</v>
+        <v>432249.2870282981</v>
       </c>
       <c r="R155" t="n">
-        <v>6485757.051572653</v>
+        <v>6485833.28914346</v>
       </c>
       <c r="S155" t="n">
         <v>2</v>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20255,7 +20255,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>103259400</v>
+        <v>103256641</v>
       </c>
       <c r="B156" t="n">
         <v>96334</v>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -20310,10 +20310,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>432249.2870282981</v>
+        <v>432257.5981462331</v>
       </c>
       <c r="R156" t="n">
-        <v>6485833.28914346</v>
+        <v>6485829.487139624</v>
       </c>
       <c r="S156" t="n">
         <v>2</v>
@@ -20345,7 +20345,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -20382,7 +20382,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>103256641</v>
+        <v>103257725</v>
       </c>
       <c r="B157" t="n">
         <v>96334</v>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -20437,10 +20437,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>432257.5981462331</v>
+        <v>432266.5682742132</v>
       </c>
       <c r="R157" t="n">
-        <v>6485829.487139624</v>
+        <v>6485833.51269153</v>
       </c>
       <c r="S157" t="n">
         <v>2</v>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -20509,7 +20509,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103257725</v>
+        <v>103257345</v>
       </c>
       <c r="B158" t="n">
         <v>96334</v>
@@ -20544,7 +20544,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -20564,10 +20564,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>432266.5682742132</v>
+        <v>432230.5621987951</v>
       </c>
       <c r="R158" t="n">
-        <v>6485833.51269153</v>
+        <v>6485840.406999109</v>
       </c>
       <c r="S158" t="n">
         <v>2</v>
@@ -20599,7 +20599,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20636,7 +20636,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103257345</v>
+        <v>103257167</v>
       </c>
       <c r="B159" t="n">
         <v>96334</v>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -20691,13 +20691,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>432230.5621987951</v>
+        <v>432260.5848650308</v>
       </c>
       <c r="R159" t="n">
-        <v>6485840.406999109</v>
+        <v>6485820.551309</v>
       </c>
       <c r="S159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20763,7 +20763,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103257167</v>
+        <v>103256741</v>
       </c>
       <c r="B160" t="n">
         <v>96334</v>
@@ -20798,7 +20798,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -20818,13 +20818,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>432260.5848650308</v>
+        <v>432274.5277380867</v>
       </c>
       <c r="R160" t="n">
-        <v>6485820.551309</v>
+        <v>6485839.646124027</v>
       </c>
       <c r="S160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -20890,7 +20890,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>103256741</v>
+        <v>103256549</v>
       </c>
       <c r="B161" t="n">
         <v>96334</v>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -20945,13 +20945,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>432274.5277380867</v>
+        <v>432267.533719931</v>
       </c>
       <c r="R161" t="n">
-        <v>6485839.646124027</v>
+        <v>6485828.792622661</v>
       </c>
       <c r="S161" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21017,7 +21017,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>103256549</v>
+        <v>103256602</v>
       </c>
       <c r="B162" t="n">
         <v>96334</v>
@@ -21052,7 +21052,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -21072,13 +21072,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>432267.533719931</v>
+        <v>432253.762558274</v>
       </c>
       <c r="R162" t="n">
-        <v>6485828.792622661</v>
+        <v>6485819.624172981</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21144,7 +21144,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>103256602</v>
+        <v>103257228</v>
       </c>
       <c r="B163" t="n">
         <v>96334</v>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -21199,13 +21199,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>432253.762558274</v>
+        <v>432271.3059921727</v>
       </c>
       <c r="R163" t="n">
-        <v>6485819.624172981</v>
+        <v>6485834.998506625</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -21271,7 +21271,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103257228</v>
+        <v>103257997</v>
       </c>
       <c r="B164" t="n">
         <v>96334</v>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -21326,10 +21326,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>432271.3059921727</v>
+        <v>432196.1416656945</v>
       </c>
       <c r="R164" t="n">
-        <v>6485834.998506625</v>
+        <v>6485787.697968244</v>
       </c>
       <c r="S164" t="n">
         <v>2</v>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21398,7 +21398,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>103257997</v>
+        <v>103259528</v>
       </c>
       <c r="B165" t="n">
         <v>96334</v>
@@ -21433,7 +21433,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -21453,10 +21453,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>432196.1416656945</v>
+        <v>432257.1651534633</v>
       </c>
       <c r="R165" t="n">
-        <v>6485787.697968244</v>
+        <v>6485834.72059215</v>
       </c>
       <c r="S165" t="n">
         <v>2</v>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -21525,7 +21525,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>103259528</v>
+        <v>103258965</v>
       </c>
       <c r="B166" t="n">
         <v>96334</v>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -21580,13 +21580,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>432257.1651534633</v>
+        <v>432251.1194357427</v>
       </c>
       <c r="R166" t="n">
-        <v>6485834.72059215</v>
+        <v>6485848.412680772</v>
       </c>
       <c r="S166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -21652,7 +21652,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103258965</v>
+        <v>103273272</v>
       </c>
       <c r="B167" t="n">
         <v>96334</v>
@@ -21687,7 +21687,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -21707,10 +21707,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>432251.1194357427</v>
+        <v>432242.8875994325</v>
       </c>
       <c r="R167" t="n">
-        <v>6485848.412680772</v>
+        <v>6485796.295421477</v>
       </c>
       <c r="S167" t="n">
         <v>4</v>
@@ -21737,22 +21737,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -21779,7 +21779,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103273272</v>
+        <v>103272215</v>
       </c>
       <c r="B168" t="n">
         <v>96334</v>
@@ -21814,7 +21814,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -21834,13 +21834,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>432242.8875994325</v>
+        <v>432266.7662532481</v>
       </c>
       <c r="R168" t="n">
-        <v>6485796.295421477</v>
+        <v>6485814.695774876</v>
       </c>
       <c r="S168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -21879,7 +21879,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -21906,7 +21906,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103272215</v>
+        <v>103273585</v>
       </c>
       <c r="B169" t="n">
         <v>96334</v>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -21961,10 +21961,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>432266.7662532481</v>
+        <v>432253.815819026</v>
       </c>
       <c r="R169" t="n">
-        <v>6485814.695774876</v>
+        <v>6485792.44807999</v>
       </c>
       <c r="S169" t="n">
         <v>2</v>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -22033,7 +22033,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>103273585</v>
+        <v>103275225</v>
       </c>
       <c r="B170" t="n">
         <v>96334</v>
@@ -22068,7 +22068,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -22078,20 +22078,20 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>432253.815819026</v>
+        <v>432257.4696651782</v>
       </c>
       <c r="R170" t="n">
-        <v>6485792.44807999</v>
+        <v>6485761.551255709</v>
       </c>
       <c r="S170" t="n">
         <v>2</v>
@@ -22123,7 +22123,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22160,7 +22160,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>103275225</v>
+        <v>103272988</v>
       </c>
       <c r="B171" t="n">
         <v>96334</v>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -22205,20 +22205,20 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>432257.4696651782</v>
+        <v>432224.8566541995</v>
       </c>
       <c r="R171" t="n">
-        <v>6485761.551255709</v>
+        <v>6485783.019903477</v>
       </c>
       <c r="S171" t="n">
         <v>2</v>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22287,7 +22287,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>103272988</v>
+        <v>103275363</v>
       </c>
       <c r="B172" t="n">
         <v>96334</v>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -22342,10 +22342,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>432224.8566541995</v>
+        <v>432248.8610387372</v>
       </c>
       <c r="R172" t="n">
-        <v>6485783.019903477</v>
+        <v>6485778.423568772</v>
       </c>
       <c r="S172" t="n">
         <v>2</v>
@@ -22377,7 +22377,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -22414,7 +22414,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>103275363</v>
+        <v>103273450</v>
       </c>
       <c r="B173" t="n">
         <v>96334</v>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -22469,13 +22469,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>432248.8610387372</v>
+        <v>432251.7583623823</v>
       </c>
       <c r="R173" t="n">
-        <v>6485778.423568772</v>
+        <v>6485794.574090446</v>
       </c>
       <c r="S173" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -22541,7 +22541,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>103273450</v>
+        <v>103272727</v>
       </c>
       <c r="B174" t="n">
         <v>96334</v>
@@ -22576,7 +22576,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -22592,17 +22592,17 @@
       <c r="L174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>432251.7583623823</v>
+        <v>432275.8621243032</v>
       </c>
       <c r="R174" t="n">
-        <v>6485794.574090446</v>
+        <v>6485795.724825109</v>
       </c>
       <c r="S174" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -22668,7 +22668,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103272727</v>
+        <v>103275168</v>
       </c>
       <c r="B175" t="n">
         <v>96334</v>
@@ -22703,7 +22703,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -22719,17 +22719,17 @@
       <c r="L175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>432275.8621243032</v>
+        <v>432243.7445166245</v>
       </c>
       <c r="R175" t="n">
-        <v>6485795.724825109</v>
+        <v>6485785.305957633</v>
       </c>
       <c r="S175" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -22795,7 +22795,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>103275168</v>
+        <v>103272041</v>
       </c>
       <c r="B176" t="n">
         <v>96334</v>
@@ -22830,7 +22830,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -22850,10 +22850,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>432243.7445166245</v>
+        <v>432265.5395532835</v>
       </c>
       <c r="R176" t="n">
-        <v>6485785.305957633</v>
+        <v>6485834.57568248</v>
       </c>
       <c r="S176" t="n">
         <v>2</v>
@@ -22885,7 +22885,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -22922,7 +22922,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103272041</v>
+        <v>103272249</v>
       </c>
       <c r="B177" t="n">
         <v>96334</v>
@@ -22957,7 +22957,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -22977,10 +22977,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>432265.5395532835</v>
+        <v>432275.3576164559</v>
       </c>
       <c r="R177" t="n">
-        <v>6485834.57568248</v>
+        <v>6485827.089470007</v>
       </c>
       <c r="S177" t="n">
         <v>2</v>
@@ -23012,7 +23012,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23049,7 +23049,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>103272249</v>
+        <v>103272879</v>
       </c>
       <c r="B178" t="n">
         <v>96334</v>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -23100,17 +23100,17 @@
       <c r="L178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>432275.3576164559</v>
+        <v>432267.9748894515</v>
       </c>
       <c r="R178" t="n">
-        <v>6485827.089470007</v>
+        <v>6485793.770878337</v>
       </c>
       <c r="S178" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -23149,7 +23149,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23176,7 +23176,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>103272879</v>
+        <v>103274736</v>
       </c>
       <c r="B179" t="n">
         <v>96334</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -23227,17 +23227,17 @@
       <c r="L179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>432267.9748894515</v>
+        <v>432246.605688389</v>
       </c>
       <c r="R179" t="n">
-        <v>6485793.770878337</v>
+        <v>6485799.366672672</v>
       </c>
       <c r="S179" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23303,7 +23303,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>103274736</v>
+        <v>103274059</v>
       </c>
       <c r="B180" t="n">
         <v>96334</v>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -23358,10 +23358,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>432246.605688389</v>
+        <v>432212.2975063801</v>
       </c>
       <c r="R180" t="n">
-        <v>6485799.366672672</v>
+        <v>6485843.85880534</v>
       </c>
       <c r="S180" t="n">
         <v>2</v>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23430,7 +23430,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>103274059</v>
+        <v>103272548</v>
       </c>
       <c r="B181" t="n">
         <v>96334</v>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -23485,13 +23485,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>432212.2975063801</v>
+        <v>432254.6556636693</v>
       </c>
       <c r="R181" t="n">
-        <v>6485843.85880534</v>
+        <v>6485810.724547338</v>
       </c>
       <c r="S181" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23557,7 +23557,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>103272548</v>
+        <v>103274704</v>
       </c>
       <c r="B182" t="n">
         <v>96334</v>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -23612,13 +23612,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>432254.6556636693</v>
+        <v>432253.7444758158</v>
       </c>
       <c r="R182" t="n">
-        <v>6485810.724547338</v>
+        <v>6485818.57929049</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -23684,7 +23684,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103274704</v>
+        <v>103272328</v>
       </c>
       <c r="B183" t="n">
         <v>96334</v>
@@ -23739,10 +23739,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>432253.7444758158</v>
+        <v>432259.4566971283</v>
       </c>
       <c r="R183" t="n">
-        <v>6485818.57929049</v>
+        <v>6485815.8674508</v>
       </c>
       <c r="S183" t="n">
         <v>2</v>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23811,7 +23811,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>103272328</v>
+        <v>103273556</v>
       </c>
       <c r="B184" t="n">
         <v>96334</v>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -23866,13 +23866,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>432259.4566971283</v>
+        <v>432252.0667758805</v>
       </c>
       <c r="R184" t="n">
-        <v>6485815.8674508</v>
+        <v>6485842.647749359</v>
       </c>
       <c r="S184" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -23938,7 +23938,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103273556</v>
+        <v>103274591</v>
       </c>
       <c r="B185" t="n">
         <v>96334</v>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -23993,13 +23993,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>432252.0667758805</v>
+        <v>432240.5689926533</v>
       </c>
       <c r="R185" t="n">
-        <v>6485842.647749359</v>
+        <v>6485813.581342359</v>
       </c>
       <c r="S185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24065,7 +24065,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>103274591</v>
+        <v>103272284</v>
       </c>
       <c r="B186" t="n">
         <v>96334</v>
@@ -24100,7 +24100,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -24120,13 +24120,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>432240.5689926533</v>
+        <v>432252.625340549</v>
       </c>
       <c r="R186" t="n">
-        <v>6485813.581342359</v>
+        <v>6485814.417873605</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24192,7 +24192,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103272284</v>
+        <v>103271623</v>
       </c>
       <c r="B187" t="n">
         <v>96334</v>
@@ -24227,7 +24227,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -24243,14 +24243,14 @@
       <c r="L187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>432252.625340549</v>
+        <v>432275.6550601376</v>
       </c>
       <c r="R187" t="n">
-        <v>6485814.417873605</v>
+        <v>6485814.019389195</v>
       </c>
       <c r="S187" t="n">
         <v>2</v>
@@ -24282,7 +24282,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -24319,7 +24319,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>103271623</v>
+        <v>103273070</v>
       </c>
       <c r="B188" t="n">
         <v>96334</v>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -24370,14 +24370,14 @@
       <c r="L188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>432275.6550601376</v>
+        <v>432238.7365312605</v>
       </c>
       <c r="R188" t="n">
-        <v>6485814.019389195</v>
+        <v>6485798.457674608</v>
       </c>
       <c r="S188" t="n">
         <v>2</v>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24419,7 +24419,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24446,7 +24446,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>103273070</v>
+        <v>103275031</v>
       </c>
       <c r="B189" t="n">
         <v>96334</v>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -24497,14 +24497,14 @@
       <c r="L189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>432238.7365312605</v>
+        <v>432263.2181327323</v>
       </c>
       <c r="R189" t="n">
-        <v>6485798.457674608</v>
+        <v>6485760.929180594</v>
       </c>
       <c r="S189" t="n">
         <v>2</v>
@@ -24536,7 +24536,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24573,7 +24573,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>103275031</v>
+        <v>103275074</v>
       </c>
       <c r="B190" t="n">
         <v>96334</v>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -24628,10 +24628,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>432263.2181327323</v>
+        <v>432250.9908350741</v>
       </c>
       <c r="R190" t="n">
-        <v>6485760.929180594</v>
+        <v>6485780.477121521</v>
       </c>
       <c r="S190" t="n">
         <v>2</v>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24700,7 +24700,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>103275074</v>
+        <v>103429045</v>
       </c>
       <c r="B191" t="n">
         <v>96334</v>
@@ -24735,7 +24735,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -24751,14 +24751,14 @@
       <c r="L191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>432250.9908350741</v>
+        <v>432266.6487398344</v>
       </c>
       <c r="R191" t="n">
-        <v>6485780.477121521</v>
+        <v>6485807.904025332</v>
       </c>
       <c r="S191" t="n">
         <v>2</v>
@@ -24785,22 +24785,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24827,7 +24827,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>103429045</v>
+        <v>103271550</v>
       </c>
       <c r="B192" t="n">
         <v>96334</v>
@@ -24862,7 +24862,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -24878,17 +24878,17 @@
       <c r="L192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>432266.6487398344</v>
+        <v>432267.6413107914</v>
       </c>
       <c r="R192" t="n">
-        <v>6485807.904025332</v>
+        <v>6485804.75125562</v>
       </c>
       <c r="S192" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24912,22 +24912,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-08-30</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24954,7 +24954,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>103271550</v>
+        <v>103274827</v>
       </c>
       <c r="B193" t="n">
         <v>96334</v>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -25005,17 +25005,17 @@
       <c r="L193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>432267.6413107914</v>
+        <v>432240.6684654304</v>
       </c>
       <c r="R193" t="n">
-        <v>6485804.75125562</v>
+        <v>6485819.328200064</v>
       </c>
       <c r="S193" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25081,7 +25081,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>103274827</v>
+        <v>103288446</v>
       </c>
       <c r="B194" t="n">
         <v>96334</v>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -25136,13 +25136,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>432240.6684654304</v>
+        <v>432212.5843832528</v>
       </c>
       <c r="R194" t="n">
-        <v>6485819.328200064</v>
+        <v>6485799.955642235</v>
       </c>
       <c r="S194" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -25166,22 +25166,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25208,7 +25208,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>103288446</v>
+        <v>103288715</v>
       </c>
       <c r="B195" t="n">
         <v>96334</v>
@@ -25243,7 +25243,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
@@ -25263,13 +25263,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>432212.5843832528</v>
+        <v>432225.8323093976</v>
       </c>
       <c r="R195" t="n">
-        <v>6485799.955642235</v>
+        <v>6485809.133058465</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25335,7 +25335,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>103288715</v>
+        <v>103289071</v>
       </c>
       <c r="B196" t="n">
         <v>96334</v>
@@ -25370,7 +25370,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
@@ -25390,13 +25390,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>432225.8323093976</v>
+        <v>432247.8242961877</v>
       </c>
       <c r="R196" t="n">
-        <v>6485809.133058465</v>
+        <v>6485809.274976367</v>
       </c>
       <c r="S196" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25462,7 +25462,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>103289071</v>
+        <v>103288672</v>
       </c>
       <c r="B197" t="n">
         <v>96334</v>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -25517,13 +25517,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>432247.8242961877</v>
+        <v>432240.4966487583</v>
       </c>
       <c r="R197" t="n">
-        <v>6485809.274976367</v>
+        <v>6485809.401804202</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25589,7 +25589,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>103288672</v>
+        <v>103289147</v>
       </c>
       <c r="B198" t="n">
         <v>96334</v>
@@ -25624,7 +25624,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -25644,13 +25644,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>432240.4966487583</v>
+        <v>432228.9094182872</v>
       </c>
       <c r="R198" t="n">
-        <v>6485809.401804202</v>
+        <v>6485805.421590333</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25716,7 +25716,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>103289147</v>
+        <v>103287407</v>
       </c>
       <c r="B199" t="n">
         <v>96334</v>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -25771,13 +25771,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>432228.9094182872</v>
+        <v>432243.9705797723</v>
       </c>
       <c r="R199" t="n">
-        <v>6485805.421590333</v>
+        <v>6485798.367079639</v>
       </c>
       <c r="S199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -25816,7 +25816,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25843,7 +25843,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>103287407</v>
+        <v>103287372</v>
       </c>
       <c r="B200" t="n">
         <v>96334</v>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -25898,13 +25898,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>432243.9705797723</v>
+        <v>432240.1349285647</v>
       </c>
       <c r="R200" t="n">
-        <v>6485798.367079639</v>
+        <v>6485788.504046717</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>103287372</v>
+        <v>103288246</v>
       </c>
       <c r="B201" t="n">
         <v>96334</v>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -26025,13 +26025,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>432240.1349285647</v>
+        <v>432242.9056847495</v>
       </c>
       <c r="R201" t="n">
-        <v>6485788.504046717</v>
+        <v>6485797.340309916</v>
       </c>
       <c r="S201" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -26070,7 +26070,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26097,7 +26097,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>103288246</v>
+        <v>103287903</v>
       </c>
       <c r="B202" t="n">
         <v>96334</v>
@@ -26132,7 +26132,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -26152,13 +26152,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>432242.9056847495</v>
+        <v>432252.5258853729</v>
       </c>
       <c r="R202" t="n">
-        <v>6485797.340309916</v>
+        <v>6485808.671008832</v>
       </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26224,7 +26224,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>103287903</v>
+        <v>103290245</v>
       </c>
       <c r="B203" t="n">
         <v>96334</v>
@@ -26259,7 +26259,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -26279,10 +26279,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>432252.5258853729</v>
+        <v>432258.6811099342</v>
       </c>
       <c r="R203" t="n">
-        <v>6485808.671008832</v>
+        <v>6485831.558783957</v>
       </c>
       <c r="S203" t="n">
         <v>2</v>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -26351,7 +26351,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>103290245</v>
+        <v>103289334</v>
       </c>
       <c r="B204" t="n">
         <v>96334</v>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -26406,13 +26406,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>432258.6811099342</v>
+        <v>432221.7988554602</v>
       </c>
       <c r="R204" t="n">
-        <v>6485831.558783957</v>
+        <v>6485818.087067345</v>
       </c>
       <c r="S204" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26478,7 +26478,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>103289334</v>
+        <v>103288868</v>
       </c>
       <c r="B205" t="n">
         <v>96334</v>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -26533,13 +26533,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>432221.7988554602</v>
+        <v>432241.777489557</v>
       </c>
       <c r="R205" t="n">
-        <v>6485818.087067345</v>
+        <v>6485792.656428487</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26605,7 +26605,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>103288868</v>
+        <v>103290751</v>
       </c>
       <c r="B206" t="n">
         <v>96334</v>
@@ -26640,7 +26640,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -26660,10 +26660,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>432241.777489557</v>
+        <v>432257.4806167439</v>
       </c>
       <c r="R206" t="n">
-        <v>6485792.656428487</v>
+        <v>6485822.695415544</v>
       </c>
       <c r="S206" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26705,7 +26705,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26732,7 +26732,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>103290751</v>
+        <v>103290886</v>
       </c>
       <c r="B207" t="n">
         <v>96334</v>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -26787,10 +26787,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>432257.4806167439</v>
+        <v>432243.5838819765</v>
       </c>
       <c r="R207" t="n">
-        <v>6485822.695415544</v>
+        <v>6485836.523425706</v>
       </c>
       <c r="S207" t="n">
         <v>2</v>
@@ -26859,7 +26859,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>103290886</v>
+        <v>103430082</v>
       </c>
       <c r="B208" t="n">
         <v>96334</v>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -26910,14 +26910,14 @@
       <c r="L208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Säter Högsmon, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>432243.5838819765</v>
+        <v>432286.0410481391</v>
       </c>
       <c r="R208" t="n">
-        <v>6485836.523425706</v>
+        <v>6485778.825486699</v>
       </c>
       <c r="S208" t="n">
         <v>2</v>
@@ -26944,22 +26944,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26986,7 +26986,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>103430082</v>
+        <v>103429226</v>
       </c>
       <c r="B209" t="n">
         <v>96334</v>
@@ -27021,12 +27021,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -27041,10 +27041,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>432286.0410481391</v>
+        <v>432277.9286310925</v>
       </c>
       <c r="R209" t="n">
-        <v>6485778.825486699</v>
+        <v>6485794.121272818</v>
       </c>
       <c r="S209" t="n">
         <v>2</v>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27113,7 +27113,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>103429226</v>
+        <v>103431421</v>
       </c>
       <c r="B210" t="n">
         <v>96334</v>
@@ -27148,12 +27148,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -27168,10 +27168,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>432277.9286310925</v>
+        <v>432265.393128803</v>
       </c>
       <c r="R210" t="n">
-        <v>6485794.121272818</v>
+        <v>6485765.594992966</v>
       </c>
       <c r="S210" t="n">
         <v>2</v>
@@ -27203,7 +27203,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -27213,7 +27213,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27240,7 +27240,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>103431421</v>
+        <v>103431266</v>
       </c>
       <c r="B211" t="n">
         <v>96334</v>
@@ -27275,7 +27275,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -27295,13 +27295,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>432265.393128803</v>
+        <v>432276.9985126653</v>
       </c>
       <c r="R211" t="n">
-        <v>6485765.594992966</v>
+        <v>6485770.620252518</v>
       </c>
       <c r="S211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -27367,7 +27367,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>103431266</v>
+        <v>103430116</v>
       </c>
       <c r="B212" t="n">
         <v>96334</v>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -27422,13 +27422,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>432276.9985126653</v>
+        <v>432276.9270109005</v>
       </c>
       <c r="R212" t="n">
-        <v>6485770.620252518</v>
+        <v>6485796.751604024</v>
       </c>
       <c r="S212" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27494,7 +27494,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>103430116</v>
+        <v>103430420</v>
       </c>
       <c r="B213" t="n">
         <v>96334</v>
@@ -27529,7 +27529,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -27549,13 +27549,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>432276.9270109005</v>
+        <v>432279.832460779</v>
       </c>
       <c r="R213" t="n">
-        <v>6485796.751604024</v>
+        <v>6485783.113704092</v>
       </c>
       <c r="S213" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -27621,7 +27621,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>103430420</v>
+        <v>103430253</v>
       </c>
       <c r="B214" t="n">
         <v>96334</v>
@@ -27656,7 +27656,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -27676,13 +27676,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>432279.832460779</v>
+        <v>432287.9268357529</v>
       </c>
       <c r="R214" t="n">
-        <v>6485783.113704092</v>
+        <v>6485766.772983584</v>
       </c>
       <c r="S214" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -27748,7 +27748,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>103430253</v>
+        <v>103431381</v>
       </c>
       <c r="B215" t="n">
         <v>96334</v>
@@ -27783,7 +27783,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -27803,10 +27803,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>432287.9268357529</v>
+        <v>432281.2942312295</v>
       </c>
       <c r="R215" t="n">
-        <v>6485766.772983584</v>
+        <v>6485776.81718425</v>
       </c>
       <c r="S215" t="n">
         <v>2</v>
@@ -27838,7 +27838,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -27875,7 +27875,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>103431381</v>
+        <v>103431850</v>
       </c>
       <c r="B216" t="n">
         <v>96334</v>
@@ -27910,7 +27910,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -27930,10 +27930,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>432281.2942312295</v>
+        <v>432273.0914419788</v>
       </c>
       <c r="R216" t="n">
-        <v>6485776.81718425</v>
+        <v>6485786.888536702</v>
       </c>
       <c r="S216" t="n">
         <v>2</v>
@@ -27965,7 +27965,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28002,7 +28002,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>103431850</v>
+        <v>103429730</v>
       </c>
       <c r="B217" t="n">
         <v>96334</v>
@@ -28037,7 +28037,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -28057,13 +28057,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>432273.0914419788</v>
+        <v>432259.8254756255</v>
       </c>
       <c r="R217" t="n">
-        <v>6485786.888536702</v>
+        <v>6485776.666015873</v>
       </c>
       <c r="S217" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28129,7 +28129,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>103429730</v>
+        <v>103430980</v>
       </c>
       <c r="B218" t="n">
         <v>96334</v>
@@ -28164,7 +28164,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>432259.8254756255</v>
+        <v>432290.4625544801</v>
       </c>
       <c r="R218" t="n">
-        <v>6485776.666015873</v>
+        <v>6485762.025681825</v>
       </c>
       <c r="S218" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -28256,7 +28256,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>103430980</v>
+        <v>103430058</v>
       </c>
       <c r="B219" t="n">
         <v>96334</v>
@@ -28291,7 +28291,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -28311,13 +28311,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>432290.4625544801</v>
+        <v>432284.6967529705</v>
       </c>
       <c r="R219" t="n">
-        <v>6485762.025681825</v>
+        <v>6485791.913790111</v>
       </c>
       <c r="S219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -28383,7 +28383,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>103430058</v>
+        <v>103429384</v>
       </c>
       <c r="B220" t="n">
         <v>96334</v>
@@ -28418,7 +28418,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -28438,13 +28438,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>432284.6967529705</v>
+        <v>432292.818236876</v>
       </c>
       <c r="R220" t="n">
-        <v>6485791.913790111</v>
+        <v>6485777.140456984</v>
       </c>
       <c r="S220" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -28510,7 +28510,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>103429384</v>
+        <v>103431340</v>
       </c>
       <c r="B221" t="n">
         <v>96334</v>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -28565,10 +28565,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>432292.818236876</v>
+        <v>432279.1192602272</v>
       </c>
       <c r="R221" t="n">
-        <v>6485777.140456984</v>
+        <v>6485772.151376968</v>
       </c>
       <c r="S221" t="n">
         <v>2</v>
@@ -28600,7 +28600,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -28610,7 +28610,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -28637,7 +28637,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>103431340</v>
+        <v>103431293</v>
       </c>
       <c r="B222" t="n">
         <v>96334</v>
@@ -28672,7 +28672,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -28692,10 +28692,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>432279.1192602272</v>
+        <v>432262.1713130459</v>
       </c>
       <c r="R222" t="n">
-        <v>6485772.151376968</v>
+        <v>6485760.947293817</v>
       </c>
       <c r="S222" t="n">
         <v>2</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -28737,7 +28737,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -28764,7 +28764,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>103431293</v>
+        <v>103430790</v>
       </c>
       <c r="B223" t="n">
         <v>96334</v>
@@ -28799,7 +28799,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -28819,13 +28819,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>432262.1713130459</v>
+        <v>432294.9299388815</v>
       </c>
       <c r="R223" t="n">
-        <v>6485760.947293817</v>
+        <v>6485778.149140608</v>
       </c>
       <c r="S223" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -28891,7 +28891,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>103430891</v>
+        <v>103431640</v>
       </c>
       <c r="B224" t="n">
         <v>96334</v>
@@ -28926,7 +28926,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -28946,13 +28946,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>432276.9894745808</v>
+        <v>432273.6961952645</v>
       </c>
       <c r="R224" t="n">
-        <v>6485770.097804811</v>
+        <v>6485791.581488307</v>
       </c>
       <c r="S224" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29018,7 +29018,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>103430790</v>
+        <v>103431517</v>
       </c>
       <c r="B225" t="n">
         <v>96334</v>
@@ -29053,7 +29053,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -29073,13 +29073,13 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>432294.9299388815</v>
+        <v>432274.0297928923</v>
       </c>
       <c r="R225" t="n">
-        <v>6485778.149140608</v>
+        <v>6485780.601075176</v>
       </c>
       <c r="S225" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29145,7 +29145,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>103431640</v>
+        <v>103430515</v>
       </c>
       <c r="B226" t="n">
         <v>96334</v>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -29200,10 +29200,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>432273.6961952645</v>
+        <v>432287.0697895117</v>
       </c>
       <c r="R226" t="n">
-        <v>6485791.581488307</v>
+        <v>6485777.762486539</v>
       </c>
       <c r="S226" t="n">
         <v>2</v>
@@ -29235,7 +29235,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -29272,7 +29272,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>103431517</v>
+        <v>103432429</v>
       </c>
       <c r="B227" t="n">
         <v>96334</v>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -29327,10 +29327,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>432274.0297928923</v>
+        <v>432274.2820471794</v>
       </c>
       <c r="R227" t="n">
-        <v>6485780.601075176</v>
+        <v>6485764.91859836</v>
       </c>
       <c r="S227" t="n">
         <v>2</v>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -29399,7 +29399,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>103430515</v>
+        <v>103432312</v>
       </c>
       <c r="B228" t="n">
         <v>96334</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -29454,13 +29454,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>432287.0697895117</v>
+        <v>432270.2303577231</v>
       </c>
       <c r="R228" t="n">
-        <v>6485777.762486539</v>
+        <v>6485772.827759717</v>
       </c>
       <c r="S228" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -29526,7 +29526,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>103432429</v>
+        <v>103430649</v>
       </c>
       <c r="B229" t="n">
         <v>96334</v>
@@ -29561,7 +29561,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -29581,10 +29581,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>432274.2820471794</v>
+        <v>432295.2635980461</v>
       </c>
       <c r="R229" t="n">
-        <v>6485764.91859836</v>
+        <v>6485767.168693206</v>
       </c>
       <c r="S229" t="n">
         <v>2</v>
@@ -29616,7 +29616,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -29653,7 +29653,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>103432312</v>
+        <v>103430597</v>
       </c>
       <c r="B230" t="n">
         <v>96334</v>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -29708,13 +29708,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>432270.2303577231</v>
+        <v>432289.2537844398</v>
       </c>
       <c r="R230" t="n">
-        <v>6485772.827759717</v>
+        <v>6485782.950737335</v>
       </c>
       <c r="S230" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -29780,7 +29780,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>103430649</v>
+        <v>103478422</v>
       </c>
       <c r="B231" t="n">
         <v>96334</v>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -29831,14 +29831,14 @@
       <c r="L231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>432295.2635980461</v>
+        <v>432274.1941480445</v>
       </c>
       <c r="R231" t="n">
-        <v>6485767.168693206</v>
+        <v>6485850.626372254</v>
       </c>
       <c r="S231" t="n">
         <v>2</v>
@@ -29865,22 +29865,22 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29907,7 +29907,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>103430597</v>
+        <v>103473677</v>
       </c>
       <c r="B232" t="n">
         <v>96334</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -29962,13 +29962,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>432289.2537844398</v>
+        <v>432290.1824294464</v>
       </c>
       <c r="R232" t="n">
-        <v>6485782.950737335</v>
+        <v>6485745.829735505</v>
       </c>
       <c r="S232" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -29992,22 +29992,22 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30034,7 +30034,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>103478422</v>
+        <v>103478363</v>
       </c>
       <c r="B233" t="n">
         <v>96334</v>
@@ -30069,7 +30069,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -30089,10 +30089,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>432274.1941480445</v>
+        <v>432264.1049514066</v>
       </c>
       <c r="R233" t="n">
-        <v>6485850.626372254</v>
+        <v>6485842.439431504</v>
       </c>
       <c r="S233" t="n">
         <v>2</v>
@@ -30124,7 +30124,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30161,7 +30161,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>103473677</v>
+        <v>103473396</v>
       </c>
       <c r="B234" t="n">
         <v>96334</v>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -30216,13 +30216,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>432290.1824294464</v>
+        <v>432287.6015168622</v>
       </c>
       <c r="R234" t="n">
-        <v>6485745.829735505</v>
+        <v>6485747.964804256</v>
       </c>
       <c r="S234" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -30261,7 +30261,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -30288,7 +30288,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>103478363</v>
+        <v>103479895</v>
       </c>
       <c r="B235" t="n">
         <v>96334</v>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -30343,10 +30343,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>432264.1049514066</v>
+        <v>432248.66416709</v>
       </c>
       <c r="R235" t="n">
-        <v>6485842.439431504</v>
+        <v>6485827.551364766</v>
       </c>
       <c r="S235" t="n">
         <v>2</v>
@@ -30378,7 +30378,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -30388,7 +30388,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -30415,7 +30415,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>103473396</v>
+        <v>103481629</v>
       </c>
       <c r="B236" t="n">
         <v>96334</v>
@@ -30450,7 +30450,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -30466,17 +30466,17 @@
       <c r="L236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Säter Högsmon, Skövde, Vg</t>
+          <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>432287.6015168622</v>
+        <v>432242.6445185435</v>
       </c>
       <c r="R236" t="n">
-        <v>6485747.964804256</v>
+        <v>6485812.50022033</v>
       </c>
       <c r="S236" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -30542,7 +30542,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>103479895</v>
+        <v>103499712</v>
       </c>
       <c r="B237" t="n">
         <v>96334</v>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -30597,10 +30597,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>432248.66416709</v>
+        <v>432195.5473036259</v>
       </c>
       <c r="R237" t="n">
-        <v>6485827.551364766</v>
+        <v>6485813.838286112</v>
       </c>
       <c r="S237" t="n">
         <v>2</v>
@@ -30627,22 +30627,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -30669,7 +30669,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>103481629</v>
+        <v>103497911</v>
       </c>
       <c r="B238" t="n">
         <v>96334</v>
@@ -30704,7 +30704,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -30724,13 +30724,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>432242.6445185435</v>
+        <v>432217.8546140154</v>
       </c>
       <c r="R238" t="n">
-        <v>6485812.50022033</v>
+        <v>6485801.95478707</v>
       </c>
       <c r="S238" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -30754,22 +30754,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30796,7 +30796,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>103499712</v>
+        <v>103498589</v>
       </c>
       <c r="B239" t="n">
         <v>96334</v>
@@ -30831,7 +30831,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -30851,10 +30851,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>432195.5473036259</v>
+        <v>432240.8120647831</v>
       </c>
       <c r="R239" t="n">
-        <v>6485813.838286112</v>
+        <v>6485797.376547629</v>
       </c>
       <c r="S239" t="n">
         <v>2</v>
@@ -30886,7 +30886,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30896,7 +30896,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30923,7 +30923,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>103497911</v>
+        <v>103497574</v>
       </c>
       <c r="B240" t="n">
         <v>96334</v>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -30978,10 +30978,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>432217.8546140154</v>
+        <v>432232.1753071275</v>
       </c>
       <c r="R240" t="n">
-        <v>6485801.95478707</v>
+        <v>6485782.37060057</v>
       </c>
       <c r="S240" t="n">
         <v>2</v>
@@ -31013,7 +31013,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -31023,7 +31023,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -31050,10 +31050,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>103498589</v>
+        <v>103500165</v>
       </c>
       <c r="B241" t="n">
-        <v>96334</v>
+        <v>87558</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -31062,53 +31062,48 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>3483</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rutbläcksvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coprinopsis picacea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>432240.8120647831</v>
+        <v>432191.5501214426</v>
       </c>
       <c r="R241" t="n">
-        <v>6485797.376547629</v>
+        <v>6485824.882079905</v>
       </c>
       <c r="S241" t="n">
         <v>2</v>
@@ -31140,7 +31135,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -31150,7 +31145,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -31177,7 +31172,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>103497574</v>
+        <v>103500842</v>
       </c>
       <c r="B242" t="n">
         <v>96334</v>
@@ -31212,7 +31207,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -31232,13 +31227,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>432232.1753071275</v>
+        <v>432227.3561076017</v>
       </c>
       <c r="R242" t="n">
-        <v>6485782.37060057</v>
+        <v>6485776.18279109</v>
       </c>
       <c r="S242" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -31267,7 +31262,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -31277,7 +31272,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -31304,10 +31299,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>103500165</v>
+        <v>103497539</v>
       </c>
       <c r="B243" t="n">
-        <v>87558</v>
+        <v>96334</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -31316,51 +31311,56 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3483</v>
+        <v>220787</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>432191.5501214426</v>
+        <v>432206.1664642375</v>
       </c>
       <c r="R243" t="n">
-        <v>6485824.882079905</v>
+        <v>6485761.91675933</v>
       </c>
       <c r="S243" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -31426,7 +31426,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>103500842</v>
+        <v>103499792</v>
       </c>
       <c r="B244" t="n">
         <v>96334</v>
@@ -31461,7 +31461,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -31481,13 +31481,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>432227.3561076017</v>
+        <v>432211.5918549802</v>
       </c>
       <c r="R244" t="n">
-        <v>6485776.18279109</v>
+        <v>6485803.108430768</v>
       </c>
       <c r="S244" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -31553,7 +31553,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>103497539</v>
+        <v>103496834</v>
       </c>
       <c r="B245" t="n">
         <v>96334</v>
@@ -31588,7 +31588,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -31608,13 +31608,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>432206.1664642375</v>
+        <v>432206.952250028</v>
       </c>
       <c r="R245" t="n">
-        <v>6485761.91675933</v>
+        <v>6485777.058683844</v>
       </c>
       <c r="S245" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -31653,7 +31653,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -31680,10 +31680,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>103499792</v>
+        <v>103498666</v>
       </c>
       <c r="B246" t="n">
-        <v>96334</v>
+        <v>57577</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -31692,25 +31692,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -31720,25 +31720,30 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>432211.5918549802</v>
+        <v>432210.8603715596</v>
       </c>
       <c r="R246" t="n">
-        <v>6485803.108430768</v>
+        <v>6485791.101277514</v>
       </c>
       <c r="S246" t="n">
         <v>2</v>
@@ -31770,7 +31775,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -31780,7 +31785,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -31807,7 +31812,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>103496834</v>
+        <v>103496623</v>
       </c>
       <c r="B247" t="n">
         <v>96334</v>
@@ -31842,7 +31847,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -31862,13 +31867,13 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>432206.952250028</v>
+        <v>432220.9859948303</v>
       </c>
       <c r="R247" t="n">
-        <v>6485777.058683844</v>
+        <v>6485801.37796888</v>
       </c>
       <c r="S247" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -31897,7 +31902,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -31907,7 +31912,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -31934,10 +31939,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>103498666</v>
+        <v>103978677</v>
       </c>
       <c r="B248" t="n">
-        <v>57577</v>
+        <v>90008</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -31950,21 +31955,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>208249</v>
+        <v>6031</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -31974,30 +31979,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>432210.8603715596</v>
+        <v>432253.5184448363</v>
       </c>
       <c r="R248" t="n">
-        <v>6485791.101277514</v>
+        <v>6485805.518235884</v>
       </c>
       <c r="S248" t="n">
         <v>2</v>
@@ -32024,22 +32019,22 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -32066,7 +32061,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>103496623</v>
+        <v>103324190</v>
       </c>
       <c r="B249" t="n">
         <v>96334</v>
@@ -32099,35 +32094,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Skövde, Vg</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>432220.9859948303</v>
+        <v>432446.7436843051</v>
       </c>
       <c r="R249" t="n">
-        <v>6485801.37796888</v>
+        <v>6485868.026016678</v>
       </c>
       <c r="S249" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -32151,22 +32133,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -32181,26 +32163,26 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Karin Nielsen</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Karin Nielsen</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>103978677</v>
+        <v>103497415</v>
       </c>
       <c r="B250" t="n">
-        <v>90008</v>
+        <v>57549</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32209,21 +32191,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6031</v>
+        <v>208245</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -32233,20 +32215,30 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>Säter Högsmon 2, Skövde, Vg</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>432253.5184448363</v>
+        <v>432214.9662010632</v>
       </c>
       <c r="R250" t="n">
-        <v>6485805.518235884</v>
+        <v>6485786.326763283</v>
       </c>
       <c r="S250" t="n">
         <v>2</v>
@@ -32273,22 +32265,22 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -32315,10 +32307,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>103324190</v>
+        <v>111399311</v>
       </c>
       <c r="B251" t="n">
-        <v>96334</v>
+        <v>96348</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -32348,22 +32340,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Skövde, Vg</t>
+          <t>Högsmon (Högsmon), Vg</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>432446.7436843051</v>
+        <v>432241.1535342821</v>
       </c>
       <c r="R251" t="n">
-        <v>6485868.026016678</v>
+        <v>6485756.60757375</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -32387,22 +32387,22 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32417,85 +32417,79 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Gitte Jutvik Guterstam</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Gitte Jutvik Guterstam</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>103497415</v>
+        <v>111419836</v>
       </c>
       <c r="B252" t="n">
-        <v>57549</v>
+        <v>96348</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>vilande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Säter Högsmon 2, Skövde, Vg</t>
+          <t>Högsmon (Högsmon), Vg</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>432214.9662010632</v>
+        <v>432211.3915150585</v>
       </c>
       <c r="R252" t="n">
-        <v>6485786.326763283</v>
+        <v>6485761.303672196</v>
       </c>
       <c r="S252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -32519,22 +32513,22 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32549,19 +32543,19 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Karin Nielsen</t>
+          <t>Birgit Nielsen</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Karin Nielsen</t>
+          <t>Birgit Nielsen</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>111399311</v>
+        <v>111419064</v>
       </c>
       <c r="B253" t="n">
         <v>96348</v>
@@ -32596,7 +32590,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -32604,17 +32598,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Högsmon (Högsmon), Vg</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>432241.1535342821</v>
+        <v>432220.2894824292</v>
       </c>
       <c r="R253" t="n">
-        <v>6485756.60757375</v>
+        <v>6485761.149603307</v>
       </c>
       <c r="S253" t="n">
         <v>1</v>
@@ -32641,22 +32639,22 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32683,10 +32681,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>111419836</v>
+        <v>113689368</v>
       </c>
       <c r="B254" t="n">
-        <v>96348</v>
+        <v>97650</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -32718,32 +32716,30 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Högsmon (Högsmon), Vg</t>
+          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>432211.3915150585</v>
+        <v>432683</v>
       </c>
       <c r="R254" t="n">
-        <v>6485761.303672196</v>
+        <v>6485874</v>
       </c>
       <c r="S254" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -32767,22 +32763,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32791,28 +32777,34 @@
       <c r="AE254" t="b">
         <v>0</v>
       </c>
+      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>Blandbarrskog</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Birgit Nielsen</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Birgit Nielsen</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>111419064</v>
+        <v>113689369</v>
       </c>
       <c r="B255" t="n">
-        <v>96348</v>
+        <v>97650</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -32844,32 +32836,30 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Högsmon (Högsmon), Vg</t>
+          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>432220.2894824292</v>
+        <v>432662</v>
       </c>
       <c r="R255" t="n">
-        <v>6485761.149603307</v>
+        <v>6485797</v>
       </c>
       <c r="S255" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -32893,22 +32883,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -32917,395 +32897,27 @@
       <c r="AE255" t="b">
         <v>0</v>
       </c>
+      <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="b">
         <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>Blandbarrskog</t>
+        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Gitte Jutvik Guterstam</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Gitte Jutvik Guterstam</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>111418425</v>
-      </c>
-      <c r="B256" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E256" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>Högsmon (Högsmon), Vg</t>
-        </is>
-      </c>
-      <c r="Q256" t="n">
-        <v>432220</v>
-      </c>
-      <c r="R256" t="n">
-        <v>6485761</v>
-      </c>
-      <c r="S256" t="n">
-        <v>1</v>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>Skövde</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>Binneberg</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>En blomma, en rosett</t>
-        </is>
-      </c>
-      <c r="AD256" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE256" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF256" t="inlineStr"/>
-      <c r="AG256" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT256" t="inlineStr"/>
-      <c r="AW256" t="inlineStr">
-        <is>
-          <t>Gitte Jutvik Guterstam</t>
-        </is>
-      </c>
-      <c r="AX256" t="inlineStr">
-        <is>
-          <t>Gitte Jutvik Guterstam</t>
-        </is>
-      </c>
-      <c r="AY256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>113689368</v>
-      </c>
-      <c r="B257" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E257" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
-        </is>
-      </c>
-      <c r="Q257" t="n">
-        <v>432683</v>
-      </c>
-      <c r="R257" t="n">
-        <v>6485874</v>
-      </c>
-      <c r="S257" t="n">
-        <v>10</v>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>Skövde</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>Binneberg</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AD257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF257" t="inlineStr"/>
-      <c r="AG257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>Blandbarrskog</t>
-        </is>
-      </c>
-      <c r="AT257" t="inlineStr"/>
-      <c r="AW257" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX257" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>113689369</v>
-      </c>
-      <c r="B258" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E258" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>Binneberg, Kärrtorp 7, väster om, Vg</t>
-        </is>
-      </c>
-      <c r="Q258" t="n">
-        <v>432662</v>
-      </c>
-      <c r="R258" t="n">
-        <v>6485797</v>
-      </c>
-      <c r="S258" t="n">
-        <v>10</v>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>Skövde</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>Binneberg</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AD258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF258" t="inlineStr"/>
-      <c r="AG258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>Blandbarrskog</t>
-        </is>
-      </c>
-      <c r="AT258" t="inlineStr"/>
-      <c r="AW258" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX258" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
